--- a/InputData/elec/ESUfRaLCD/Elec Sources Used for Rlbty and Lst Cst Dsptch.xlsx
+++ b/InputData/elec/ESUfRaLCD/Elec Sources Used for Rlbty and Lst Cst Dsptch.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://energyinnovation.sharepoint.com/sites/IndonesiaEPS/Shared Documents/Updated Indonesia InputData files/elec/ESUfRaLCD/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mary Francis Swint\Vensim\eps-indonesia\InputData\elec\ESUfRaLCD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{26578C50-7F18-C947-84CA-18CC1CD39ED8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C69A538-F81F-4351-B6A1-2CEA52171BC8}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42EFB418-28F1-4F4A-86CD-BAF6BF5C108C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{4A7A9C5C-85FC-43FE-AB1B-A2C5DC00E496}"/>
+    <workbookView xWindow="-38520" yWindow="-5880" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{4A7A9C5C-85FC-43FE-AB1B-A2C5DC00E496}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="61">
   <si>
     <t xml:space="preserve">Sources: </t>
   </si>
@@ -760,7 +760,7 @@
   <sheetPr>
     <tabColor theme="4" tint="-0.499984740745262"/>
   </sheetPr>
-  <dimension ref="A1:C84"/>
+  <dimension ref="A1:C85"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="30.453125" bestFit="1" customWidth="1"/>
@@ -780,164 +780,167 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="B2" t="str">
         <f>IF(A2="","",CONCATENATE(A2," es"))</f>
-        <v>natural gas combined cycle es</v>
+        <v>hard coal es</v>
       </c>
       <c r="C2" t="str">
         <f>IF(A2="","",CONCATENATE(A2," power plants"))</f>
-        <v>natural gas combined cycle power plants</v>
+        <v>hard coal power plants</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B3" t="str">
-        <f t="shared" ref="B3:B25" si="0">IF(A3="","",CONCATENATE(A3," es"))</f>
-        <v>onshore wind es</v>
+        <f>IF(A3="","",CONCATENATE(A3," es"))</f>
+        <v>natural gas combined cycle es</v>
       </c>
       <c r="C3" t="str">
-        <f t="shared" ref="C3:C70" si="1">IF(A3="","",CONCATENATE(A3," power plants"))</f>
-        <v>onshore wind power plants</v>
+        <f>IF(A3="","",CONCATENATE(A3," power plants"))</f>
+        <v>natural gas combined cycle power plants</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B4" t="str">
-        <f t="shared" si="0"/>
-        <v>solar PV es</v>
+        <f t="shared" ref="B4:B26" si="0">IF(A4="","",CONCATENATE(A4," es"))</f>
+        <v>onshore wind es</v>
       </c>
       <c r="C4" t="str">
-        <f t="shared" si="1"/>
-        <v>solar PV power plants</v>
+        <f t="shared" ref="C4:C71" si="1">IF(A4="","",CONCATENATE(A4," power plants"))</f>
+        <v>onshore wind power plants</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B5" t="str">
         <f t="shared" si="0"/>
-        <v>petroleum es</v>
+        <v>solar PV es</v>
       </c>
       <c r="C5" t="str">
         <f t="shared" si="1"/>
-        <v>petroleum power plants</v>
+        <v>solar PV power plants</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B6" t="str">
         <f t="shared" si="0"/>
-        <v>natural gas peaker es</v>
+        <v>petroleum es</v>
       </c>
       <c r="C6" t="str">
         <f t="shared" si="1"/>
-        <v>natural gas peaker power plants</v>
+        <v>petroleum power plants</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B7" t="str">
         <f t="shared" si="0"/>
-        <v>small modular reactor es</v>
+        <v>natural gas peaker es</v>
       </c>
       <c r="C7" t="str">
         <f t="shared" si="1"/>
-        <v>small modular reactor power plants</v>
+        <v>natural gas peaker power plants</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>55</v>
-      </c>
-      <c r="B8" t="s">
-        <v>53</v>
+        <v>34</v>
+      </c>
+      <c r="B8" t="str">
+        <f t="shared" si="0"/>
+        <v>small modular reactor es</v>
       </c>
       <c r="C8" t="str">
         <f t="shared" si="1"/>
-        <v>hard coal w ccs power plants</v>
+        <v>small modular reactor power plants</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C9" t="str">
         <f t="shared" si="1"/>
-        <v>natural gas combined cycle w ccs power plants</v>
+        <v>hard coal w ccs power plants</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="C10" t="str">
         <f t="shared" si="1"/>
-        <v>biomass w ccs power plants</v>
+        <v>natural gas combined cycle w ccs power plants</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C11" t="str">
         <f t="shared" si="1"/>
-        <v>lignite w ccs power plants</v>
+        <v>biomass w ccs power plants</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>35</v>
-      </c>
-      <c r="B12" t="str">
-        <f t="shared" si="0"/>
-        <v>hydrogen combustion turbine es</v>
+        <v>58</v>
+      </c>
+      <c r="B12" t="s">
+        <v>26</v>
       </c>
       <c r="C12" t="str">
         <f t="shared" si="1"/>
-        <v>hydrogen combustion turbine power plants</v>
+        <v>lignite w ccs power plants</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" t="str">
+        <f t="shared" si="0"/>
+        <v>hydrogen combustion turbine es</v>
+      </c>
+      <c r="C13" t="str">
+        <f t="shared" si="1"/>
+        <v>hydrogen combustion turbine power plants</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
         <v>36</v>
       </c>
-      <c r="B13" t="str">
+      <c r="B14" t="str">
         <f t="shared" si="0"/>
         <v>hydrogen combined cycle es</v>
       </c>
-      <c r="C13" t="str">
+      <c r="C14" t="str">
         <f t="shared" si="1"/>
         <v>hydrogen combined cycle power plants</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B14" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="C14" t="str">
-        <f t="shared" si="1"/>
-        <v/>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
@@ -1051,6 +1054,10 @@
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B26" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="C26" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1322,13 +1329,13 @@
     </row>
     <row r="71" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C71" t="str">
-        <f t="shared" ref="C71:C84" si="2">IF(A71="","",CONCATENATE(A71," power plants"))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="72" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C72" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="C72:C85" si="2">IF(A72="","",CONCATENATE(A72," power plants"))</f>
         <v/>
       </c>
     </row>
@@ -1400,6 +1407,12 @@
     </row>
     <row r="84" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C84" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="85" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C85" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -1649,15 +1662,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002041A8AB53924247A2770D65450F5227" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="90fff4f083191fe75a03dbd50c7739fc">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1659011e-6b88-4225-9a61-aaf33aaf19e8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7fee88694a371868130ae0617c69143c" ns2:_="">
     <xsd:import namespace="1659011e-6b88-4225-9a61-aaf33aaf19e8"/>
@@ -1801,6 +1805,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -1808,15 +1821,29 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D43FAB59-5026-45F2-B56A-9AD5D2941E1E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="1659011e-6b88-4225-9a61-aaf33aaf19e8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4C07F645-AD4C-42F6-963A-810FE67D4798}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D43FAB59-5026-45F2-B56A-9AD5D2941E1E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
